--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-coverage.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Coverage</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Coverage|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -372,7 +372,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -463,7 +463,7 @@
     <t>insuredPersonSymbol</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSymbol}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSymbol|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -486,7 +486,7 @@
     <t>insuredPersonNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonNumber}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonNumber|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -505,7 +505,7 @@
     <t>insuredPersonSubNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSubNumber}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSubNumber|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -700,7 +700,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -794,7 +794,7 @@
     <t>Coverage.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -931,7 +931,7 @@
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-type|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -943,7 +943,7 @@
     <t>Coverage.policyHolder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -977,7 +977,7 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1017,7 +1017,7 @@
     <t>Coverage.beneficiary</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1091,7 +1091,7 @@
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.0.1</t>
   </si>
   <si>
     <t>C03</t>
@@ -1136,7 +1136,7 @@
     <t>Coverage.payor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1236,7 +1236,7 @@
     <t>ポリシー分類、例。グループ、プラン、クラスなど / The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-class</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-class|4.0.1</t>
   </si>
   <si>
     <t>Coverage.class.value</t>
@@ -1373,7 +1373,7 @@
     <t>患者の自己負担が指定されているサービスの種類。 / The types of services to which patient copayments are specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.id</t>
@@ -1564,7 +1564,7 @@
     <t>Coverage.costToBeneficiary.value[x]</t>
   </si>
   <si>
-    <t>Quantity {SimpleQuantity}
+    <t>Quantity {SimpleQuantity|4.0.1}
 Money</t>
   </si>
   <si>
@@ -1622,7 +1622,7 @@
     <t>部品からの例外の種類またはCopaysなどの財務義務の完全な価値。 / The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.exception.period</t>
@@ -1660,7 +1660,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract)
+    <t xml:space="preserve">Reference(Contract|4.0.1)
 </t>
   </si>
   <si>
@@ -1996,7 +1996,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="110.515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.02734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2011,7 +2011,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-coverage.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Coverage|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Coverage</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -372,7 +372,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -463,7 +463,7 @@
     <t>insuredPersonSymbol</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSymbol|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSymbol}
 </t>
   </si>
   <si>
@@ -486,7 +486,7 @@
     <t>insuredPersonNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonNumber|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonNumber}
 </t>
   </si>
   <si>
@@ -505,7 +505,7 @@
     <t>insuredPersonSubNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSubNumber|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Coverage_InsuredPersonSubNumber}
 </t>
   </si>
   <si>
@@ -700,7 +700,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -794,7 +794,7 @@
     <t>Coverage.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -931,7 +931,7 @@
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-type</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -943,7 +943,7 @@
     <t>Coverage.policyHolder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -977,7 +977,7 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1017,7 +1017,7 @@
     <t>Coverage.beneficiary</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1091,7 +1091,7 @@
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
   </si>
   <si>
     <t>C03</t>
@@ -1136,7 +1136,7 @@
     <t>Coverage.payor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1236,7 +1236,7 @@
     <t>ポリシー分類、例。グループ、プラン、クラスなど / The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-class|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-class</t>
   </si>
   <si>
     <t>Coverage.class.value</t>
@@ -1373,7 +1373,7 @@
     <t>患者の自己負担が指定されているサービスの種類。 / The types of services to which patient copayments are specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.id</t>
@@ -1564,7 +1564,7 @@
     <t>Coverage.costToBeneficiary.value[x]</t>
   </si>
   <si>
-    <t>Quantity {SimpleQuantity|4.0.1}
+    <t>Quantity {SimpleQuantity}
 Money</t>
   </si>
   <si>
@@ -1622,7 +1622,7 @@
     <t>部品からの例外の種類またはCopaysなどの財務義務の完全な価値。 / The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.exception.period</t>
@@ -1660,7 +1660,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract|4.0.1)
+    <t xml:space="preserve">Reference(Contract)
 </t>
   </si>
   <si>
@@ -1996,7 +1996,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="131.02734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2011,7 +2011,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
